--- a/data/trans_dic/DCD-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,27</t>
+          <t>2,07; 6,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,5</t>
+          <t>3,48; 9,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 12,95</t>
+          <t>6,69; 12,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,96</t>
+          <t>13,81; 23,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 27,05</t>
+          <t>16,88; 26,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 20,35</t>
+          <t>13,7; 20,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 14,01</t>
+          <t>8,38; 13,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 16,3</t>
+          <t>10,76; 16,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 15,35</t>
+          <t>10,66; 15,36</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,6</t>
+          <t>3,96; 8,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,13</t>
+          <t>2,61; 6,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 15,75</t>
+          <t>8,74; 14,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,87</t>
+          <t>11,57; 17,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,02</t>
+          <t>5,2; 9,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 30,48</t>
+          <t>24,31; 30,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,21</t>
+          <t>8,33; 12,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,41</t>
+          <t>4,4; 7,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 22,03</t>
+          <t>17,08; 21,96</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,14</t>
+          <t>3,17; 8,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,01</t>
+          <t>3,34; 8,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 18,98</t>
+          <t>11,91; 19,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,77</t>
+          <t>9,19; 16,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 16,65</t>
+          <t>9,18; 17,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 30,08</t>
+          <t>22,68; 29,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,56</t>
+          <t>7,08; 11,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,52</t>
+          <t>6,89; 11,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,53</t>
+          <t>18,43; 23,72</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,22</t>
+          <t>4,95; 11,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,76</t>
+          <t>6,31; 12,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,92</t>
+          <t>11,02; 19,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 23,44</t>
+          <t>15,63; 23,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 22,22</t>
+          <t>13,89; 22,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 27,8</t>
+          <t>13,11; 27,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 16,2</t>
+          <t>11,17; 16,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 16,02</t>
+          <t>10,98; 16,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 22,18</t>
+          <t>13,64; 22,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 19,23</t>
+          <t>9,23; 19,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,9</t>
+          <t>4,96; 13,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,3</t>
+          <t>7,01; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,51; 40,23</t>
+          <t>26,71; 39,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 22,2</t>
+          <t>12,41; 22,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 21,78</t>
+          <t>8,47; 21,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,71; 28,18</t>
+          <t>19,43; 27,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 16,13</t>
+          <t>9,55; 16,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,19; 16,69</t>
+          <t>9,51; 17,01</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,16</t>
+          <t>7,27; 15,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,21</t>
+          <t>4,5; 11,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,9; 23,09</t>
+          <t>15,29; 22,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,06; 21,16</t>
+          <t>12,3; 21,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 18,11</t>
+          <t>9,56; 18,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,65; 37,85</t>
+          <t>28,68; 37,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 16,97</t>
+          <t>10,74; 16,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,62</t>
+          <t>7,67; 13,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,79</t>
+          <t>22,87; 28,72</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,2</t>
+          <t>4,59; 8,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,4</t>
+          <t>5,65; 10,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 19,11</t>
+          <t>13,24; 19,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 18,48</t>
+          <t>12,72; 18,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 15,28</t>
+          <t>9,81; 15,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,02; 36,67</t>
+          <t>12,86; 36,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,6</t>
+          <t>9,24; 12,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,99</t>
+          <t>8,58; 12,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,45; 26,78</t>
+          <t>15,02; 26,93</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,16</t>
+          <t>3,95; 7,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,76</t>
+          <t>5,0; 8,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,21</t>
+          <t>3,42; 11,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,65; 15,5</t>
+          <t>10,54; 15,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,66</t>
+          <t>9,19; 13,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,87; 25,15</t>
+          <t>19,85; 25,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 10,79</t>
+          <t>8,0; 10,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,71</t>
+          <t>7,47; 10,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,2</t>
+          <t>8,99; 17,27</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,6</t>
+          <t>5,79; 7,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,69</t>
+          <t>5,87; 7,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,79</t>
+          <t>9,71; 13,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,09; 17,6</t>
+          <t>15,1; 17,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,91; 14,25</t>
+          <t>12,0; 14,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,84; 26,3</t>
+          <t>19,47; 26,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,33</t>
+          <t>10,78; 12,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,21; 10,71</t>
+          <t>9,2; 10,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,09; 19,92</t>
+          <t>15,87; 19,86</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5392; 18469</t>
+          <t>6099; 19535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10434; 27906</t>
+          <t>10225; 27356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20750; 40346</t>
+          <t>20836; 39883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39803; 68832</t>
+          <t>39674; 67336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48392; 78103</t>
+          <t>48736; 76686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39925; 58939</t>
+          <t>39679; 59159</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49085; 81537</t>
+          <t>48791; 80859</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63185; 94956</t>
+          <t>62654; 98428</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63629; 92279</t>
+          <t>64076; 92329</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19776; 43466</t>
+          <t>20004; 44017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13529; 30825</t>
+          <t>13105; 30700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45576; 81651</t>
+          <t>45299; 76645</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60840; 93579</t>
+          <t>60577; 94012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27448; 52426</t>
+          <t>27189; 52166</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122785; 156973</t>
+          <t>125182; 157692</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85655; 125713</t>
+          <t>85727; 126924</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45792; 75986</t>
+          <t>45091; 75455</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>174825; 227616</t>
+          <t>176516; 226913</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10300; 29611</t>
+          <t>10275; 27630</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9900; 25502</t>
+          <t>10655; 26012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37156; 60002</t>
+          <t>37646; 60139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30959; 57191</t>
+          <t>31345; 57322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30626; 56010</t>
+          <t>30873; 57159</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78757; 105025</t>
+          <t>79187; 104090</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46216; 76893</t>
+          <t>47087; 77274</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45466; 75443</t>
+          <t>45125; 74639</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>121637; 156520</t>
+          <t>122610; 157803</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18963; 41942</t>
+          <t>18509; 41644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23482; 47220</t>
+          <t>23342; 46238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33740; 59130</t>
+          <t>34452; 60149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59839; 91154</t>
+          <t>60784; 92754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54758; 86041</t>
+          <t>53807; 86897</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60440; 132243</t>
+          <t>62351; 132247</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85498; 123561</t>
+          <t>85250; 124780</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82577; 121274</t>
+          <t>83148; 122074</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113065; 174810</t>
+          <t>107498; 177688</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19454; 40894</t>
+          <t>19614; 40714</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10966; 27256</t>
+          <t>10486; 27639</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12830; 25551</t>
+          <t>12531; 25450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60408; 88352</t>
+          <t>58648; 87452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26846; 48526</t>
+          <t>27135; 49153</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20042; 56369</t>
+          <t>21924; 56418</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85200; 121786</t>
+          <t>83990; 120296</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41560; 69332</t>
+          <t>41029; 69357</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40205; 73036</t>
+          <t>41617; 74418</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21000; 41526</t>
+          <t>19914; 41818</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11708; 29499</t>
+          <t>11831; 29056</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40176; 62269</t>
+          <t>41234; 61580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33784; 59264</t>
+          <t>34443; 60483</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26433; 49468</t>
+          <t>26116; 50154</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73642; 97307</t>
+          <t>73721; 96396</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61773; 93994</t>
+          <t>59488; 92472</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42732; 73058</t>
+          <t>41145; 70573</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118580; 151647</t>
+          <t>120429; 151291</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29706; 54362</t>
+          <t>30445; 54470</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37741; 68312</t>
+          <t>37070; 66340</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82512; 119317</t>
+          <t>82639; 121256</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88923; 128253</t>
+          <t>88288; 126469</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67912; 105628</t>
+          <t>67785; 106360</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>119074; 311461</t>
+          <t>109199; 310646</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>125286; 170903</t>
+          <t>125399; 171458</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>116872; 161664</t>
+          <t>115691; 165240</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>198142; 394568</t>
+          <t>221305; 396811</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30163; 55750</t>
+          <t>30798; 55771</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>39809; 68223</t>
+          <t>38939; 65559</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31474; 104097</t>
+          <t>31734; 104907</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87712; 127727</t>
+          <t>86848; 127044</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75044; 112838</t>
+          <t>75921; 114330</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>142608; 180478</t>
+          <t>142504; 179870</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>127798; 172899</t>
+          <t>128293; 174309</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>123121; 171837</t>
+          <t>119944; 167345</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>146512; 283195</t>
+          <t>147996; 284381</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>199449; 260328</t>
+          <t>198343; 256990</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>199191; 260919</t>
+          <t>199386; 259359</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>337616; 477084</t>
+          <t>336018; 476740</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>537033; 626371</t>
+          <t>537418; 624984</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>422039; 505227</t>
+          <t>425440; 510224</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>736624; 976182</t>
+          <t>722617; 975036</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>757863; 861259</t>
+          <t>753113; 862980</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>639330; 743382</t>
+          <t>638683; 741169</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1154101; 1428993</t>
+          <t>1138230; 1424504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,63</t>
+          <t>1,91; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,31</t>
+          <t>3,43; 9,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 12,81</t>
+          <t>6,65; 12,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 23,44</t>
+          <t>13,79; 23,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 26,56</t>
+          <t>16,86; 26,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 20,43</t>
+          <t>14,12; 20,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,89</t>
+          <t>8,32; 13,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,9</t>
+          <t>10,86; 16,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 15,36</t>
+          <t>11,21; 15,8</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,71</t>
+          <t>3,95; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,11</t>
+          <t>2,77; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 14,79</t>
+          <t>8,87; 15,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 17,95</t>
+          <t>11,38; 17,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,97</t>
+          <t>5,17; 9,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,31; 30,62</t>
+          <t>23,7; 30,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,33</t>
+          <t>8,43; 12,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,36</t>
+          <t>4,51; 7,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 21,96</t>
+          <t>16,88; 22,07</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,53</t>
+          <t>3,39; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,17</t>
+          <t>3,09; 8,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 19,03</t>
+          <t>11,39; 18,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 16,81</t>
+          <t>8,99; 16,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,0</t>
+          <t>8,99; 17,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,68; 29,81</t>
+          <t>22,38; 29,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,62</t>
+          <t>7,12; 11,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,4</t>
+          <t>6,85; 11,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 23,72</t>
+          <t>18,13; 23,14</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,14</t>
+          <t>5,16; 10,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,5</t>
+          <t>6,07; 12,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 19,24</t>
+          <t>10,01; 17,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 23,85</t>
+          <t>15,68; 24,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,89; 22,44</t>
+          <t>13,86; 21,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 27,8</t>
+          <t>23,33; 31,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,36</t>
+          <t>11,15; 16,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,98; 16,12</t>
+          <t>10,92; 16,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 22,54</t>
+          <t>17,49; 23,17</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 19,15</t>
+          <t>9,31; 19,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,09</t>
+          <t>4,83; 12,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,24</t>
+          <t>6,4; 13,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,71; 39,82</t>
+          <t>26,73; 39,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 22,49</t>
+          <t>12,33; 22,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 21,8</t>
+          <t>15,68; 22,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 27,83</t>
+          <t>19,49; 27,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,14</t>
+          <t>9,61; 16,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 17,01</t>
+          <t>12,31; 17,27</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,26</t>
+          <t>7,17; 14,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,04</t>
+          <t>4,44; 11,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,29; 22,84</t>
+          <t>14,91; 22,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 21,6</t>
+          <t>12,02; 21,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,36</t>
+          <t>9,72; 18,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,68; 37,5</t>
+          <t>28,21; 37,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 16,69</t>
+          <t>10,59; 16,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,16</t>
+          <t>8,15; 13,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,87; 28,72</t>
+          <t>22,2; 28,3</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,22</t>
+          <t>4,49; 8,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,1</t>
+          <t>5,84; 10,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 19,42</t>
+          <t>13,35; 19,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,72; 18,23</t>
+          <t>12,84; 18,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,39</t>
+          <t>9,83; 14,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,86; 36,58</t>
+          <t>33,04; 39,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,64</t>
+          <t>9,2; 12,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,26</t>
+          <t>8,69; 11,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,02; 26,93</t>
+          <t>24,29; 28,98</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,16</t>
+          <t>3,85; 7,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,42</t>
+          <t>4,91; 8,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,3</t>
+          <t>8,58; 12,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,54; 15,42</t>
+          <t>10,9; 15,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,84</t>
+          <t>9,12; 13,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,85; 25,06</t>
+          <t>19,51; 24,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,87</t>
+          <t>7,93; 10,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,43</t>
+          <t>7,57; 10,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,99; 17,27</t>
+          <t>14,75; 17,92</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,5</t>
+          <t>5,78; 7,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,64</t>
+          <t>5,94; 7,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,78</t>
+          <t>11,84; 14,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,1; 17,56</t>
+          <t>15,09; 17,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,39</t>
+          <t>11,92; 14,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,47; 26,27</t>
+          <t>25,49; 28,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,35</t>
+          <t>10,85; 12,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,2; 10,68</t>
+          <t>9,25; 10,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,86</t>
+          <t>19,06; 20,87</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>29917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>54355</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77627</t>
+          <t>84273</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6099; 19535</t>
+          <t>5640; 19061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10225; 27356</t>
+          <t>10067; 27099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20836; 39883</t>
+          <t>21202; 41183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39674; 67336</t>
+          <t>39619; 68484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48736; 76686</t>
+          <t>48673; 77603</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39679; 59159</t>
+          <t>44639; 65680</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48791; 80859</t>
+          <t>48396; 80336</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62654; 98428</t>
+          <t>63258; 98715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64076; 92329</t>
+          <t>71168; 100294</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>140210</t>
+          <t>146076</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>200165</t>
+          <t>207892</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20004; 44017</t>
+          <t>19966; 42318</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13105; 30700</t>
+          <t>13939; 32850</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45299; 76645</t>
+          <t>47079; 81491</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60577; 94012</t>
+          <t>59600; 93283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27189; 52166</t>
+          <t>27042; 51278</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>125182; 157692</t>
+          <t>129541; 165501</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85727; 126924</t>
+          <t>86815; 125917</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45091; 75455</t>
+          <t>46218; 75302</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>176516; 226913</t>
+          <t>181849; 237771</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47652</t>
+          <t>46709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90498</t>
+          <t>92182</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>138891</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10275; 27630</t>
+          <t>10990; 27750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10655; 26012</t>
+          <t>9851; 25479</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37646; 60139</t>
+          <t>36000; 58519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31345; 57322</t>
+          <t>30661; 56763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30873; 57159</t>
+          <t>30232; 57461</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79187; 104090</t>
+          <t>79768; 106324</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47087; 77274</t>
+          <t>47326; 77110</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45125; 74639</t>
+          <t>44887; 74405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>122610; 157803</t>
+          <t>121875; 155606</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45715</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>102073</t>
+          <t>112937</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>147788</t>
+          <t>162266</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18509; 41644</t>
+          <t>19286; 40237</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23342; 46238</t>
+          <t>22475; 46034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34452; 60149</t>
+          <t>37341; 65720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60784; 92754</t>
+          <t>60992; 93784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53807; 86897</t>
+          <t>53693; 84629</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62351; 132247</t>
+          <t>98452; 131937</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85250; 124780</t>
+          <t>85095; 123936</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83148; 122074</t>
+          <t>82700; 122231</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>107498; 177688</t>
+          <t>139040; 184231</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>63439</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19614; 40714</t>
+          <t>19792; 40879</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10486; 27639</t>
+          <t>10204; 26461</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12531; 25450</t>
+          <t>13158; 26924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58648; 87452</t>
+          <t>58707; 87722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27135; 49153</t>
+          <t>26958; 49477</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21924; 56418</t>
+          <t>35883; 52323</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83990; 120296</t>
+          <t>84235; 120574</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41029; 69357</t>
+          <t>41317; 69116</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41617; 74418</t>
+          <t>53509; 75037</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>49632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84634</t>
+          <t>86410</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134795</t>
+          <t>136042</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19914; 41818</t>
+          <t>19641; 40414</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11831; 29056</t>
+          <t>11674; 29297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41234; 61580</t>
+          <t>40356; 60113</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34443; 60483</t>
+          <t>33651; 59796</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26116; 50154</t>
+          <t>26551; 50084</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73721; 96396</t>
+          <t>74391; 98914</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59488; 92472</t>
+          <t>58669; 92571</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41145; 70573</t>
+          <t>43711; 71928</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>120429; 151291</t>
+          <t>118629; 151255</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100908</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>230688</t>
+          <t>280716</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>331596</t>
+          <t>397144</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30445; 54470</t>
+          <t>29737; 54923</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37070; 66340</t>
+          <t>38330; 67389</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82639; 121256</t>
+          <t>96093; 138236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88288; 126469</t>
+          <t>89101; 129047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67785; 106360</t>
+          <t>67961; 103015</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>109199; 310646</t>
+          <t>255089; 305079</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>125399; 171458</t>
+          <t>124789; 173351</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>115691; 165240</t>
+          <t>117161; 161316</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>221305; 396811</t>
+          <t>362343; 432340</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72402</t>
+          <t>81836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>160713</t>
+          <t>181036</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>233115</t>
+          <t>262873</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30798; 55771</t>
+          <t>29984; 55127</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38939; 65559</t>
+          <t>38248; 66202</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31734; 104907</t>
+          <t>68512; 99404</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>86848; 127044</t>
+          <t>89771; 128495</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75921; 114330</t>
+          <t>75363; 113197</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>142504; 179870</t>
+          <t>162214; 201229</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>128293; 174309</t>
+          <t>127051; 174747</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>119944; 167345</t>
+          <t>121466; 166735</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>147996; 284381</t>
+          <t>240332; 291979</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>198343; 256990</t>
+          <t>198146; 256925</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>199386; 259359</t>
+          <t>201723; 258952</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>336018; 476740</t>
+          <t>418162; 503157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>537418; 624984</t>
+          <t>536814; 626754</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>425440; 510224</t>
+          <t>422673; 503963</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>722617; 975036</t>
+          <t>952398; 1048222</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>753113; 862980</t>
+          <t>757979; 871047</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>638683; 741169</t>
+          <t>642058; 743100</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1138230; 1424504</t>
+          <t>1385950; 1517258</t>
         </is>
       </c>
     </row>
